--- a/output/vino_prezzi_2026-03-24.xlsx
+++ b/output/vino_prezzi_2026-03-24.xlsx
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>7.3</v>
+        <v>10.5</v>
       </c>
       <c r="F31" t="n">
-        <v>7.3</v>
+        <v>10.5</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2044,14 +2044,14 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>15.6</v>
+        <v>16.5</v>
       </c>
       <c r="F38" t="n">
-        <v>14.8</v>
+        <v>15.7</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3463,10 +3463,10 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>15.2</v>
+        <v>16.2</v>
       </c>
       <c r="F71" t="n">
-        <v>15.2</v>
+        <v>16.2</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
